--- a/Phase1/Test_Cases_Ayari_Tech.xlsx
+++ b/Phase1/Test_Cases_Ayari_Tech.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\Desktop\Labphase_Ayari\Ayaris-Tech-Shop-Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\Desktop\Labphase_Ayari\Ayaris-Tech-Shop-Testing\Phase1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B7F6EA-3F45-4DE8-9FE1-1D597077B27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
